--- a/Data/EXCEL/Transfer/salemon/202512/7841-salemon-202512.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202512/7841-salemon-202512.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\202512\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202512\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A7C93A6-000F-4D86-BD8D-87FB906939B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA2A445F-1C72-49A7-877C-50FDEBCF0477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="930" windowWidth="26910" windowHeight="18975" xr2:uid="{47CDFE1E-42A6-40D1-A466-06C1B4985A83}"/>
+    <workbookView xWindow="0" yWindow="1740" windowWidth="17565" windowHeight="11295" xr2:uid="{6FBCD7F8-0E60-4CB3-A50E-5178232162F7}"/>
   </bookViews>
   <sheets>
     <sheet name="7841-salemon-202512" sheetId="2" r:id="rId1"/>
@@ -1258,20 +1258,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F05E513-6E35-4A4F-8D3F-0E466F7D57B7}">
-  <dimension ref="A1:Q11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{754AF67A-9EAF-4A7E-8DAF-3F4F4A75B905}">
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="3" width="12.625" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="12.625" customWidth="1"/>
-    <col min="6" max="7" width="13.75" customWidth="1"/>
-    <col min="8" max="9" width="12.625" customWidth="1"/>
-    <col min="10" max="12" width="12" customWidth="1"/>
-    <col min="13" max="14" width="12.625" customWidth="1"/>
-    <col min="15" max="16" width="12" customWidth="1"/>
-    <col min="17" max="17" width="12.625" customWidth="1"/>
+    <col min="1" max="1" width="9.375" customWidth="1"/>
+    <col min="2" max="3" width="7.875" customWidth="1"/>
+    <col min="4" max="4" width="7.5" customWidth="1"/>
+    <col min="5" max="5" width="7.875" customWidth="1"/>
+    <col min="6" max="7" width="8.625" customWidth="1"/>
+    <col min="8" max="9" width="7.875" customWidth="1"/>
+    <col min="10" max="12" width="7.5" customWidth="1"/>
+    <col min="13" max="14" width="7.875" customWidth="1"/>
+    <col min="15" max="16" width="7.5" customWidth="1"/>
+    <col min="17" max="17" width="7.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -1424,211 +1424,211 @@
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B5" s="6">
-        <v>40.799999999999997</v>
+        <v>36.5</v>
       </c>
       <c r="C5" s="6">
-        <v>36.5</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="D5" s="6">
-        <v>41.5</v>
+        <v>38</v>
       </c>
       <c r="E5" s="6">
-        <v>36.4</v>
+        <v>35.15</v>
       </c>
       <c r="F5" s="7">
-        <v>-4.3</v>
+        <v>-0.7</v>
       </c>
       <c r="G5" s="7">
-        <v>-10.54</v>
+        <v>-1.92</v>
       </c>
       <c r="H5" s="8">
-        <v>0.56599999999999995</v>
+        <v>0.7</v>
       </c>
       <c r="I5" s="9">
-        <v>64.3</v>
+        <v>23.6</v>
       </c>
       <c r="J5" s="9">
-        <v>83.3</v>
+        <v>64.099999999999994</v>
       </c>
       <c r="K5" s="8">
-        <v>4.25</v>
+        <v>4.95</v>
       </c>
       <c r="L5" s="9">
-        <v>25.6</v>
+        <v>29.9</v>
       </c>
       <c r="M5" s="8">
-        <v>0.56599999999999995</v>
+        <v>0.7</v>
       </c>
       <c r="N5" s="9">
-        <v>64.3</v>
+        <v>23.6</v>
       </c>
       <c r="O5" s="9">
-        <v>83.3</v>
+        <v>64.099999999999994</v>
       </c>
       <c r="P5" s="8">
-        <v>4.25</v>
+        <v>4.95</v>
       </c>
       <c r="Q5" s="9">
-        <v>25.6</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B6" s="12">
-        <v>45.85</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="C6" s="12">
-        <v>40.799999999999997</v>
+        <v>36.5</v>
       </c>
       <c r="D6" s="12">
-        <v>46</v>
+        <v>41.5</v>
       </c>
       <c r="E6" s="12">
-        <v>40.299999999999997</v>
+        <v>36.4</v>
       </c>
       <c r="F6" s="13">
-        <v>-5.05</v>
+        <v>-4.3</v>
       </c>
       <c r="G6" s="13">
-        <v>-11.01</v>
+        <v>-10.54</v>
       </c>
       <c r="H6" s="14">
-        <v>0.34399999999999997</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="I6" s="15">
-        <v>12.3</v>
+        <v>64.3</v>
       </c>
       <c r="J6" s="15">
-        <v>12.4</v>
+        <v>83.3</v>
       </c>
       <c r="K6" s="14">
-        <v>3.69</v>
+        <v>4.25</v>
       </c>
       <c r="L6" s="15">
-        <v>19.8</v>
+        <v>25.6</v>
       </c>
       <c r="M6" s="14">
-        <v>0.34399999999999997</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="N6" s="15">
-        <v>12.3</v>
+        <v>64.3</v>
       </c>
       <c r="O6" s="15">
-        <v>12.4</v>
+        <v>83.3</v>
       </c>
       <c r="P6" s="14">
-        <v>3.69</v>
+        <v>4.25</v>
       </c>
       <c r="Q6" s="15">
-        <v>19.8</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B7" s="6">
-        <v>45.3</v>
+        <v>45.85</v>
       </c>
       <c r="C7" s="6">
-        <v>45.85</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="D7" s="6">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7" s="6">
-        <v>44.05</v>
-      </c>
-      <c r="F7" s="9">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="G7" s="9">
-        <v>1.21</v>
+        <v>40.299999999999997</v>
+      </c>
+      <c r="F7" s="7">
+        <v>-5.05</v>
+      </c>
+      <c r="G7" s="7">
+        <v>-11.01</v>
       </c>
       <c r="H7" s="8">
-        <v>0.307</v>
+        <v>0.34399999999999997</v>
       </c>
       <c r="I7" s="9">
-        <v>6.95</v>
+        <v>12.3</v>
       </c>
       <c r="J7" s="9">
-        <v>21</v>
+        <v>12.4</v>
       </c>
       <c r="K7" s="8">
-        <v>3.34</v>
+        <v>3.69</v>
       </c>
       <c r="L7" s="9">
-        <v>20.6</v>
+        <v>19.8</v>
       </c>
       <c r="M7" s="8">
-        <v>0.307</v>
+        <v>0.34399999999999997</v>
       </c>
       <c r="N7" s="9">
-        <v>6.95</v>
+        <v>12.3</v>
       </c>
       <c r="O7" s="9">
-        <v>21</v>
+        <v>12.4</v>
       </c>
       <c r="P7" s="8">
-        <v>3.34</v>
+        <v>3.69</v>
       </c>
       <c r="Q7" s="9">
-        <v>20.6</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B8" s="12">
-        <v>49.5</v>
+        <v>45.3</v>
       </c>
       <c r="C8" s="12">
-        <v>45.3</v>
+        <v>45.85</v>
       </c>
       <c r="D8" s="12">
-        <v>57.2</v>
+        <v>47</v>
       </c>
       <c r="E8" s="12">
-        <v>44.5</v>
-      </c>
-      <c r="F8" s="13">
-        <v>-4.2</v>
-      </c>
-      <c r="G8" s="13">
-        <v>-8.48</v>
+        <v>44.05</v>
+      </c>
+      <c r="F8" s="15">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G8" s="15">
+        <v>1.21</v>
       </c>
       <c r="H8" s="14">
-        <v>0.28699999999999998</v>
-      </c>
-      <c r="I8" s="13">
-        <v>-43.4</v>
+        <v>0.307</v>
+      </c>
+      <c r="I8" s="15">
+        <v>6.95</v>
       </c>
       <c r="J8" s="15">
-        <v>10.3</v>
+        <v>21</v>
       </c>
       <c r="K8" s="14">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="L8" s="15">
         <v>20.6</v>
       </c>
       <c r="M8" s="14">
-        <v>0.28699999999999998</v>
-      </c>
-      <c r="N8" s="13">
-        <v>-43.4</v>
+        <v>0.307</v>
+      </c>
+      <c r="N8" s="15">
+        <v>6.95</v>
       </c>
       <c r="O8" s="15">
-        <v>10.3</v>
+        <v>21</v>
       </c>
       <c r="P8" s="14">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="Q8" s="15">
         <v>20.6</v>
@@ -1636,160 +1636,213 @@
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B9" s="6">
-        <v>40.049999999999997</v>
+        <v>49.5</v>
       </c>
       <c r="C9" s="6">
-        <v>49.5</v>
+        <v>45.3</v>
       </c>
       <c r="D9" s="6">
-        <v>50.5</v>
+        <v>57.2</v>
       </c>
       <c r="E9" s="6">
-        <v>38</v>
-      </c>
-      <c r="F9" s="9">
-        <v>9.4499999999999993</v>
-      </c>
-      <c r="G9" s="9">
-        <v>23.6</v>
+        <v>44.5</v>
+      </c>
+      <c r="F9" s="7">
+        <v>-4.2</v>
+      </c>
+      <c r="G9" s="7">
+        <v>-8.48</v>
       </c>
       <c r="H9" s="8">
-        <v>0.50600000000000001</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="I9" s="7">
-        <v>-15</v>
+        <v>-43.4</v>
       </c>
       <c r="J9" s="9">
-        <v>42.5</v>
+        <v>10.3</v>
       </c>
       <c r="K9" s="8">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="L9" s="9">
-        <v>21.8</v>
+        <v>20.6</v>
       </c>
       <c r="M9" s="8">
-        <v>0.50600000000000001</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="N9" s="7">
-        <v>-15</v>
+        <v>-43.4</v>
       </c>
       <c r="O9" s="9">
-        <v>42.5</v>
+        <v>10.3</v>
       </c>
       <c r="P9" s="8">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="Q9" s="9">
-        <v>21.8</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B10" s="12">
-        <v>57.5</v>
+        <v>40.049999999999997</v>
       </c>
       <c r="C10" s="12">
-        <v>40.049999999999997</v>
+        <v>49.5</v>
       </c>
       <c r="D10" s="12">
-        <v>60</v>
+        <v>50.5</v>
       </c>
       <c r="E10" s="12">
-        <v>38.950000000000003</v>
-      </c>
-      <c r="F10" s="13">
-        <v>-17.45</v>
-      </c>
-      <c r="G10" s="13">
-        <v>-30.35</v>
+        <v>38</v>
+      </c>
+      <c r="F10" s="15">
+        <v>9.4499999999999993</v>
+      </c>
+      <c r="G10" s="15">
+        <v>23.6</v>
       </c>
       <c r="H10" s="14">
-        <v>0.59499999999999997</v>
-      </c>
-      <c r="I10" s="15">
-        <v>106.5</v>
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="I10" s="13">
+        <v>-15</v>
       </c>
       <c r="J10" s="15">
-        <v>64.5</v>
+        <v>42.5</v>
       </c>
       <c r="K10" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.75</v>
       </c>
       <c r="L10" s="15">
-        <v>17.899999999999999</v>
+        <v>21.8</v>
       </c>
       <c r="M10" s="14">
-        <v>0.59499999999999997</v>
-      </c>
-      <c r="N10" s="15">
-        <v>106.5</v>
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="N10" s="13">
+        <v>-15</v>
       </c>
       <c r="O10" s="15">
-        <v>64.5</v>
+        <v>42.5</v>
       </c>
       <c r="P10" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.75</v>
       </c>
       <c r="Q10" s="15">
-        <v>17.899999999999999</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
+        <v>45809</v>
+      </c>
+      <c r="B11" s="6">
+        <v>57.5</v>
+      </c>
+      <c r="C11" s="6">
+        <v>40.049999999999997</v>
+      </c>
+      <c r="D11" s="6">
+        <v>60</v>
+      </c>
+      <c r="E11" s="6">
+        <v>38.950000000000003</v>
+      </c>
+      <c r="F11" s="7">
+        <v>-17.45</v>
+      </c>
+      <c r="G11" s="7">
+        <v>-30.35</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="I11" s="9">
+        <v>106.5</v>
+      </c>
+      <c r="J11" s="9">
+        <v>64.5</v>
+      </c>
+      <c r="K11" s="8">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="L11" s="9">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="N11" s="9">
+        <v>106.5</v>
+      </c>
+      <c r="O11" s="9">
+        <v>64.5</v>
+      </c>
+      <c r="P11" s="8">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>17.899999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
         <v>45778</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H12" s="14">
         <v>0.28799999999999998</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J12" s="15">
         <v>20.8</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K12" s="14">
         <v>1.65</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L12" s="15">
         <v>6.94</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M12" s="14">
         <v>0.28799999999999998</v>
       </c>
-      <c r="N11" s="8" t="s">
+      <c r="N12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O12" s="15">
         <v>20.8</v>
       </c>
-      <c r="P11" s="8">
+      <c r="P12" s="14">
         <v>1.65</v>
       </c>
-      <c r="Q11" s="9">
+      <c r="Q12" s="15">
         <v>6.94</v>
       </c>
     </row>
